--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationdosage-usageduration.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationdosage-usageduration.xlsx
@@ -269,7 +269,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -344,7 +344,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>単位コードUCUMにおける実投与日数の単位。dで固定される</t>
   </si>
   <si>
-    <t>優先システムはUCUMですが、スノムCTは（慣習ユニットに）または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
